--- a/InputData/elec/FoGBPD/Fraction of Grid Batteries Produced Domestically.xlsx
+++ b/InputData/elec/FoGBPD/Fraction of Grid Batteries Produced Domestically.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\elec\FoGBPD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\FoGBPD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2714A51-C325-49C1-8EAC-664F57A297EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF661C7-B2F5-4E97-B15A-7CC3333A0E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60090" yWindow="1935" windowWidth="21600" windowHeight="15210" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="31935" yWindow="3675" windowWidth="19200" windowHeight="11205" activeTab="4" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -234,7 +234,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -259,6 +259,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1222,118 +1225,121 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.54296875" customWidth="1"/>
     <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="14">
+        <f>C2</f>
+        <v>0.62</v>
+      </c>
+      <c r="C2" s="10">
         <f>'S&amp;P'!B24</f>
-        <v>0.62</v>
-      </c>
-      <c r="C2" s="10">
-        <f>B2</f>
         <v>0.62</v>
       </c>
       <c r="D2" s="10">
@@ -1348,33 +1354,34 @@
         <f>E2</f>
         <v>0.62</v>
       </c>
-      <c r="G2" s="11">
-        <f>$F2+($K2-$F2)*(G1-$F1)/($K1-$F1)</f>
+      <c r="G2" s="10">
+        <f>F2</f>
+        <v>0.62</v>
+      </c>
+      <c r="H2" s="11">
+        <f>$G2+($L2-$G2)*(H1-$G1)/($L1-$G1)</f>
         <v>0.67826281817074652</v>
       </c>
-      <c r="H2" s="11">
-        <f t="shared" ref="H2:J2" si="0">$F2+($K2-$F2)*(H1-$F1)/($K1-$F1)</f>
+      <c r="I2" s="11">
+        <f t="shared" ref="I2:K2" si="0">$G2+($L2-$G2)*(I1-$G1)/($L1-$G1)</f>
         <v>0.73652563634149304</v>
       </c>
-      <c r="I2" s="11">
+      <c r="J2" s="11">
         <f t="shared" si="0"/>
         <v>0.79478845451223967</v>
       </c>
-      <c r="J2" s="11">
+      <c r="K2" s="11">
         <f t="shared" si="0"/>
         <v>0.85305127268298619</v>
       </c>
-      <c r="K2" s="12">
+      <c r="L2" s="12">
         <f>AVERAGE(Argonne!K32,SEIA!M33)</f>
         <v>0.91131409085373272</v>
       </c>
-      <c r="L2" s="13">
-        <f>$K2+($M2-$K2)*(L1-$K1)/($M1-$K1)</f>
+      <c r="M2" s="13">
+        <f>$L2+($N2-$L2)*(M1-$L1)/($N1-$L1)</f>
         <v>0.95565704542686636</v>
       </c>
-      <c r="M2" s="13">
-        <v>1</v>
-      </c>
       <c r="N2" s="13">
         <v>1</v>
       </c>
@@ -1427,6 +1434,9 @@
         <v>1</v>
       </c>
       <c r="AE2" s="13">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="13">
         <v>1</v>
       </c>
     </row>

--- a/InputData/elec/FoGBPD/Fraction of Grid Batteries Produced Domestically.xlsx
+++ b/InputData/elec/FoGBPD/Fraction of Grid Batteries Produced Domestically.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28816"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\FoGBPD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\elec\FoGBPD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF661C7-B2F5-4E97-B15A-7CC3333A0E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{F2714A51-C325-49C1-8EAC-664F57A297EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06554274-5189-40A9-BB2B-724AF0C82AC1}"/>
   <bookViews>
-    <workbookView xWindow="31935" yWindow="3675" windowWidth="19200" windowHeight="11205" activeTab="4" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="60090" yWindow="1935" windowWidth="21600" windowHeight="15210" firstSheet="3" activeTab="3" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="SEIA" sheetId="3" r:id="rId2"/>
     <sheet name="Argonne" sheetId="4" r:id="rId3"/>
-    <sheet name="S&amp;P" sheetId="5" r:id="rId4"/>
-    <sheet name="FoGBPD" sheetId="2" r:id="rId5"/>
+    <sheet name="FoGBPD" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,115 +39,112 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+  <si>
+    <t>FoGBPD Fraction of Grid Batteries Produced Domestically</t>
+  </si>
   <si>
     <t>Sources:</t>
   </si>
   <si>
+    <t>SEIA</t>
+  </si>
+  <si>
+    <t>Energizing American Battery Storage Manufacturing</t>
+  </si>
+  <si>
+    <t>https://seia.org/research-resources/energizing-american-battery-storage-manufacturing/</t>
+  </si>
+  <si>
+    <t>Figures 2, 3</t>
+  </si>
+  <si>
+    <t>Argonne National Laboratory</t>
+  </si>
+  <si>
+    <t>Securing Critical Minerals for the U.S. Electric Vehicle Industry</t>
+  </si>
+  <si>
+    <t>https://publications.anl.gov/anlpubs/2024/03/187907.pdf</t>
+  </si>
+  <si>
+    <t>Figure 15</t>
+  </si>
+  <si>
+    <t>Quantification of Commercially Planned Battery Component Supply in North America through 2035</t>
+  </si>
+  <si>
+    <t>https://publications.anl.gov/anlpubs/2024/03/187735.pdf</t>
+  </si>
+  <si>
+    <t>Table 4</t>
+  </si>
+  <si>
+    <t>S&amp;P Global</t>
+  </si>
+  <si>
+    <t>BriefCASE: The game of tariffs - US moves to stifle EV battery imports from mainland China</t>
+  </si>
+  <si>
+    <t>https://www.spglobal.com/mobility/en/research-analysis/briefcase-the-game-of-tariffs-ev-battery-imports.html</t>
+  </si>
+  <si>
+    <t>Figure 1</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>This variable affects what portion of newly sold grid battery capacity qualifies for Vehicle Battery Production subsidies,</t>
+  </si>
+  <si>
+    <t>if relevant. We source 2022-2030 grid battery demand projections and manufacturing capacity from three sources: SEIA, ANL, and S&amp;P.</t>
+  </si>
+  <si>
+    <t>We assume US grid battery manufacturing potential reaches 100% of demand by 2032 due to IRA incentives.</t>
+  </si>
+  <si>
+    <t>US demand for BESS</t>
+  </si>
+  <si>
+    <t>GWh</t>
+  </si>
+  <si>
+    <t>US manufacturing capacity for for battery cells</t>
+  </si>
+  <si>
+    <t>(pulled from image)</t>
+  </si>
+  <si>
+    <t>Share of capacity dedicated to non-automotive applications (primarily BESS)</t>
+  </si>
+  <si>
+    <t>* assumes the same ratio of unannounced applications will be BESS as announced applications</t>
+  </si>
+  <si>
+    <t>Approximate US manufacturing capacity for BESS</t>
+  </si>
+  <si>
+    <t>Share of US BESS demand that can be met with domestic manufacturing</t>
+  </si>
+  <si>
+    <t>Manufacturing  capacity</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
     <t>Dmnl</t>
   </si>
   <si>
-    <t>Notes:</t>
-  </si>
-  <si>
     <t>Fraction of Grid Batteries Produced Domestically</t>
-  </si>
-  <si>
-    <t>https://seia.org/research-resources/energizing-american-battery-storage-manufacturing/</t>
-  </si>
-  <si>
-    <t>SEIA</t>
-  </si>
-  <si>
-    <t>Energizing American Battery Storage Manufacturing</t>
-  </si>
-  <si>
-    <t>Figures 2, 3</t>
-  </si>
-  <si>
-    <t>This variable affects what portion of newly sold grid battery capacity qualifies for Vehicle Battery Production subsidies,</t>
-  </si>
-  <si>
-    <t>US demand for BESS</t>
-  </si>
-  <si>
-    <t>GWh</t>
-  </si>
-  <si>
-    <t>US manufacturing capacity for for battery cells</t>
-  </si>
-  <si>
-    <t>(pulled from image)</t>
-  </si>
-  <si>
-    <t>Share of capacity dedicated to non-automotive applications (primarily BESS)</t>
-  </si>
-  <si>
-    <t>Approximate US manufacturing capacity for BESS</t>
-  </si>
-  <si>
-    <t>* assumes the same ratio of unannounced applications will be BESS as announced applications</t>
-  </si>
-  <si>
-    <t>Demand</t>
-  </si>
-  <si>
-    <t>Manufacturing  capacity</t>
-  </si>
-  <si>
-    <t>https://www.spglobal.com/mobility/en/research-analysis/briefcase-the-game-of-tariffs-ev-battery-imports.html</t>
-  </si>
-  <si>
-    <t>Argonne National Laboratory</t>
-  </si>
-  <si>
-    <t>Figure 15</t>
-  </si>
-  <si>
-    <t>Securing Critical Minerals for the U.S. Electric Vehicle Industry</t>
-  </si>
-  <si>
-    <t>https://publications.anl.gov/anlpubs/2024/03/187907.pdf</t>
-  </si>
-  <si>
-    <t>Quantification of Commercially Planned Battery Component Supply in North America through 2035</t>
-  </si>
-  <si>
-    <t>https://publications.anl.gov/anlpubs/2024/03/187735.pdf</t>
-  </si>
-  <si>
-    <t>Table 4</t>
-  </si>
-  <si>
-    <t>S&amp;P Global</t>
-  </si>
-  <si>
-    <t>BriefCASE: The game of tariffs - US moves to stifle EV battery imports from mainland China</t>
-  </si>
-  <si>
-    <t>Figure 1</t>
-  </si>
-  <si>
-    <t>if relevant. We source 2022-2030 grid battery demand projections and manufacturing capacity from three sources: SEIA, ANL, and S&amp;P.</t>
-  </si>
-  <si>
-    <t>We assume US grid battery manufacturing potential reaches 100% of demand by 2032 due to IRA incentives.</t>
-  </si>
-  <si>
-    <t>Share of US BESS demand that can be met with domestic manufacturing</t>
-  </si>
-  <si>
-    <t>Current share of EV battery sourcing</t>
-  </si>
-  <si>
-    <t>FoGBPD Fraction of Grid Batteries Produced Domestically</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,7 +176,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,30 +195,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -234,7 +209,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -247,20 +222,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -468,76 +430,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>106928</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Country Sources for Lithion-ion Used in US Electric Vehicles ">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93CF438A-CB48-D04E-8FBA-86B0975D3E8B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="609600" y="180975"/>
-          <a:ext cx="5000625" cy="3367653"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -575,7 +471,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -681,7 +577,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -823,7 +719,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -832,167 +728,167 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="101.26953125" customWidth="1"/>
+    <col min="2" max="2" width="101.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="A9" s="1"/>
-      <c r="B9" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B9" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="1"/>
       <c r="B10" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2">
       <c r="A11" s="1"/>
       <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="1"/>
       <c r="B12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="1"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2">
       <c r="A15" s="1"/>
-      <c r="B15" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B15" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2">
       <c r="A17" s="1"/>
       <c r="B17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="1"/>
       <c r="B18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="1"/>
       <c r="B19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2">
       <c r="A21" s="1"/>
-      <c r="B21" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="1"/>
       <c r="B22" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2">
       <c r="A23" s="1"/>
       <c r="B23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="1"/>
       <c r="B24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="1"/>
       <c r="B25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1003,14 +899,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8456871-96FC-47A8-BE1A-65358738DEAC}">
   <dimension ref="L2:O33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="2" spans="12:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="12:14">
       <c r="L2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="12:14" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="12:14">
       <c r="L3">
         <v>2022</v>
       </c>
@@ -1018,10 +914,10 @@
         <v>18</v>
       </c>
       <c r="N3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="12:14" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="12:14">
       <c r="L4">
         <v>2030</v>
       </c>
@@ -1029,15 +925,15 @@
         <v>119</v>
       </c>
       <c r="N4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="12:15" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="12:15">
       <c r="L21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="12:15" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="12:15">
       <c r="L22">
         <v>2022</v>
       </c>
@@ -1045,10 +941,10 @@
         <v>60</v>
       </c>
       <c r="N22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="12:15" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="12:15">
       <c r="L23">
         <v>2030</v>
       </c>
@@ -1056,18 +952,18 @@
         <v>773</v>
       </c>
       <c r="N23" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="O23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="12:15" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="12:15">
       <c r="L25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="12:15" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="12:15">
       <c r="L26">
         <v>2030</v>
       </c>
@@ -1076,17 +972,17 @@
         <v>0.13333333333333333</v>
       </c>
     </row>
-    <row r="27" spans="12:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="12:15">
       <c r="L27" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="12:15" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="12:15">
       <c r="L29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="12:15" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="12:15">
       <c r="L30">
         <v>2030</v>
       </c>
@@ -1095,15 +991,15 @@
         <v>103.06666666666666</v>
       </c>
       <c r="N30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="12:15" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="12:15">
       <c r="L32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="12:13" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="12:13">
       <c r="L33">
         <v>2030</v>
       </c>
@@ -1121,14 +1017,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B49FB018-EAB2-4AB3-B95C-024DA6C229C7}">
   <dimension ref="J6:O32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="6" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="14:15">
       <c r="N6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="14:15" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="14:15">
       <c r="N7">
         <v>2022</v>
       </c>
@@ -1137,7 +1033,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="14:15">
       <c r="N8">
         <v>2030</v>
       </c>
@@ -1146,12 +1042,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="10:12">
       <c r="J27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="10:12" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="10:12">
       <c r="J28">
         <v>2022</v>
       </c>
@@ -1160,10 +1056,10 @@
         <v>13.5</v>
       </c>
       <c r="L28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="10:12" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="10:12">
       <c r="J29">
         <v>2030</v>
       </c>
@@ -1171,15 +1067,15 @@
         <v>115</v>
       </c>
       <c r="L29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="10:12" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="10:12">
       <c r="J31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="10:12" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="10:12">
       <c r="J32">
         <v>2030</v>
       </c>
@@ -1195,252 +1091,379 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13AB29A9-70CB-4471-AE81-9A64EFDA202F}">
-  <dimension ref="B21:B24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B24" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB58F1CD-3AD5-4A1E-8AA0-C74AF29D4BF2}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="31.54296875" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="B1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H1">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="I1">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="J1">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="K1">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="L1">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="M1">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="N1">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="O1">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="P1">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="Q1">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="R1">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="S1">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="T1">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="U1">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="V1">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="W1">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="X1">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="Y1">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="Z1">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="AA1">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="AB1">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="AC1">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="AD1">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AE1">
-        <v>2049</v>
-      </c>
-      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" s="3" customFormat="1" ht="30.75">
       <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14">
-        <f>C2</f>
-        <v>0.62</v>
-      </c>
-      <c r="C2" s="10">
-        <f>'S&amp;P'!B24</f>
-        <v>0.62</v>
-      </c>
-      <c r="D2" s="10">
-        <f>C2</f>
-        <v>0.62</v>
-      </c>
-      <c r="E2" s="10">
-        <f>D2</f>
-        <v>0.62</v>
-      </c>
-      <c r="F2" s="10">
-        <f>E2</f>
-        <v>0.62</v>
-      </c>
-      <c r="G2" s="10">
-        <f>F2</f>
-        <v>0.62</v>
-      </c>
-      <c r="H2" s="11">
-        <f>$G2+($L2-$G2)*(H1-$G1)/($L1-$G1)</f>
-        <v>0.67826281817074652</v>
-      </c>
-      <c r="I2" s="11">
-        <f t="shared" ref="I2:K2" si="0">$G2+($L2-$G2)*(I1-$G1)/($L1-$G1)</f>
-        <v>0.73652563634149304</v>
-      </c>
-      <c r="J2" s="11">
-        <f t="shared" si="0"/>
-        <v>0.79478845451223967</v>
-      </c>
-      <c r="K2" s="11">
-        <f t="shared" si="0"/>
-        <v>0.85305127268298619</v>
-      </c>
-      <c r="L2" s="12">
-        <f>AVERAGE(Argonne!K32,SEIA!M33)</f>
-        <v>0.91131409085373272</v>
-      </c>
-      <c r="M2" s="13">
-        <f>$L2+($N2-$L2)*(M1-$L1)/($N1-$L1)</f>
-        <v>0.95565704542686636</v>
-      </c>
-      <c r="N2" s="13">
-        <v>1</v>
-      </c>
-      <c r="O2" s="13">
-        <v>1</v>
-      </c>
-      <c r="P2" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="13">
-        <v>1</v>
-      </c>
-      <c r="R2" s="13">
-        <v>1</v>
-      </c>
-      <c r="S2" s="13">
-        <v>1</v>
-      </c>
-      <c r="T2" s="13">
-        <v>1</v>
-      </c>
-      <c r="U2" s="13">
-        <v>1</v>
-      </c>
-      <c r="V2" s="13">
-        <v>1</v>
-      </c>
-      <c r="W2" s="13">
-        <v>1</v>
-      </c>
-      <c r="X2" s="13">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="13">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="13">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="13">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="13">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="13">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="13">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="13">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="B2" s="9">
+        <v>0</v>
+      </c>
+      <c r="C2" s="9">
+        <v>0</v>
+      </c>
+      <c r="D2" s="9">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9">
+        <v>0</v>
+      </c>
+      <c r="G2" s="9">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9">
+        <v>0</v>
+      </c>
+      <c r="I2" s="9">
+        <v>0</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0</v>
+      </c>
+      <c r="K2" s="9">
+        <v>0</v>
+      </c>
+      <c r="L2" s="9">
+        <v>0</v>
+      </c>
+      <c r="M2" s="9">
+        <v>0</v>
+      </c>
+      <c r="N2" s="9">
+        <v>0</v>
+      </c>
+      <c r="O2" s="9">
+        <v>0</v>
+      </c>
+      <c r="P2" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="9">
+        <v>0</v>
+      </c>
+      <c r="R2" s="9">
+        <v>0</v>
+      </c>
+      <c r="S2" s="9">
+        <v>0</v>
+      </c>
+      <c r="T2" s="9">
+        <v>0</v>
+      </c>
+      <c r="U2" s="9">
+        <v>0</v>
+      </c>
+      <c r="V2" s="9">
+        <v>0</v>
+      </c>
+      <c r="W2" s="9">
+        <v>0</v>
+      </c>
+      <c r="X2" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
+    <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1659011e-6b88-4225-9a61-aaf33aaf19e8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60BA8072-8EA2-489F-8FAA-915C148F3C08}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CBEA3EE-0453-43D0-A6CD-1E20C43B89E9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EB9E03C-B02E-4F62-B9A9-88B9D2318808}"/>
 </file>
--- a/InputData/elec/FoGBPD/Fraction of Grid Batteries Produced Domestically.xlsx
+++ b/InputData/elec/FoGBPD/Fraction of Grid Batteries Produced Domestically.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\elec\FoGBPD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Indonesia EPS\InputData\elec\FoGBPD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{F2714A51-C325-49C1-8EAC-664F57A297EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06554274-5189-40A9-BB2B-724AF0C82AC1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D20EC2-E10A-4D68-925A-7B8D70B61632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60090" yWindow="1935" windowWidth="21600" windowHeight="15210" firstSheet="3" activeTab="3" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="38190" yWindow="1815" windowWidth="23235" windowHeight="13365" firstSheet="3" activeTab="3" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -431,9 +431,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -471,7 +471,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -577,7 +577,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -719,7 +719,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -728,17 +728,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="101.28515625" customWidth="1"/>
+    <col min="2" max="2" width="101.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -746,147 +746,147 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -899,14 +899,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8456871-96FC-47A8-BE1A-65358738DEAC}">
   <dimension ref="L2:O33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="12:14">
+    <row r="2" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="12:14">
+    <row r="3" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L3">
         <v>2022</v>
       </c>
@@ -917,7 +917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="12:14">
+    <row r="4" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L4">
         <v>2030</v>
       </c>
@@ -928,12 +928,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="12:15">
+    <row r="21" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="12:15">
+    <row r="22" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L22">
         <v>2022</v>
       </c>
@@ -944,7 +944,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="12:15">
+    <row r="23" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L23">
         <v>2030</v>
       </c>
@@ -958,12 +958,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="12:15">
+    <row r="25" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L25" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="12:15">
+    <row r="26" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L26">
         <v>2030</v>
       </c>
@@ -972,17 +972,17 @@
         <v>0.13333333333333333</v>
       </c>
     </row>
-    <row r="27" spans="12:15">
+    <row r="27" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L27" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="12:15">
+    <row r="29" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L29" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="12:15">
+    <row r="30" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L30">
         <v>2030</v>
       </c>
@@ -994,12 +994,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="12:15">
+    <row r="32" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L32" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="12:13">
+    <row r="33" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L33">
         <v>2030</v>
       </c>
@@ -1017,14 +1017,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B49FB018-EAB2-4AB3-B95C-024DA6C229C7}">
   <dimension ref="J6:O32"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="6" spans="14:15">
+    <row r="6" spans="14:15" x14ac:dyDescent="0.3">
       <c r="N6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="14:15">
+    <row r="7" spans="14:15" x14ac:dyDescent="0.3">
       <c r="N7">
         <v>2022</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="14:15">
+    <row r="8" spans="14:15" x14ac:dyDescent="0.3">
       <c r="N8">
         <v>2030</v>
       </c>
@@ -1042,12 +1042,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="10:12">
+    <row r="27" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J27" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="10:12">
+    <row r="28" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J28">
         <v>2022</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="10:12">
+    <row r="29" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J29">
         <v>2030</v>
       </c>
@@ -1070,12 +1070,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="10:12">
+    <row r="31" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="10:12">
+    <row r="32" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J32">
         <v>2030</v>
       </c>
@@ -1095,109 +1095,112 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="31.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>31</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="3" customFormat="1" ht="30.75">
+    <row r="2" spans="1:32" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>32</v>
       </c>
@@ -1289,6 +1292,9 @@
         <v>0</v>
       </c>
       <c r="AE2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1307,12 +1313,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -1456,14 +1456,43 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60BA8072-8EA2-489F-8FAA-915C148F3C08}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60BA8072-8EA2-489F-8FAA-915C148F3C08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CBEA3EE-0453-43D0-A6CD-1E20C43B89E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EB9E03C-B02E-4F62-B9A9-88B9D2318808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EB9E03C-B02E-4F62-B9A9-88B9D2318808}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CBEA3EE-0453-43D0-A6CD-1E20C43B89E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>